--- a/sample_bulk_tasks.xlsx
+++ b/sample_bulk_tasks.xlsx
@@ -1,41 +1,161 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Project\Maurya technologies\fakhri-it-services\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B100E4D-C229-41E1-8466-5DC75AD7E173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="43">
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Website SEO Audit</t>
+  </si>
+  <si>
+    <t>Complete SEO audit for the main website including keywords and backlink analysis.</t>
+  </si>
+  <si>
+    <t>To Do</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Digital Goods</t>
+  </si>
+  <si>
+    <t>Atul Bangre</t>
+  </si>
+  <si>
+    <t>Mobile App UI Design</t>
+  </si>
+  <si>
+    <t>Design the new landing page for the mobile application in Figma.</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Alex Smith</t>
+  </si>
+  <si>
+    <t>Sarang Dev</t>
+  </si>
+  <si>
+    <t>Database Migration</t>
+  </si>
+  <si>
+    <t>Migrate the legacy database to the new MongoDB cluster.</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>Fakhri IT</t>
+  </si>
+  <si>
+    <t>Client Onboarding</t>
+  </si>
+  <si>
+    <t>Set up the workspace and accounts for the new client project.</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>2026-02-15</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>API Documentation</t>
+  </si>
+  <si>
+    <t>Update the Swagger documentation for the latest API endpoints.</t>
+  </si>
+  <si>
+    <t>In Review</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Security Patching</t>
+  </si>
+  <si>
+    <t>Apply the latest security patches to the production servers.</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +185,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,194 +524,508 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Title</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Due Date</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Week</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Client</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Owner</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Website SEO Audit</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Complete SEO audit for the main website including keywords and backlink analysis.</v>
-      </c>
-      <c r="C2" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="D2" t="str">
-        <v>High</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="F2" t="str">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" t="str">
-        <v>Digital Goods</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Atul Bangre</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Mobile App UI Design</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Design the new landing page for the mobile application in Figma.</v>
-      </c>
-      <c r="C3" t="str">
-        <v>In Progress</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026-03-05</v>
-      </c>
-      <c r="F3" t="str">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="G3" t="str">
-        <v>Alex Smith</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Sarang Dev</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Database Migration</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Migrate the legacy database to the new MongoDB cluster.</v>
-      </c>
-      <c r="C4" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="D4" t="str">
-        <v>High</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2026-02-28</v>
-      </c>
-      <c r="F4" t="str">
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="G4" t="str">
-        <v>Fakhri IT</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Atul Bangre</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Client Onboarding</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Set up the workspace and accounts for the new client project.</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Low</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="F5" t="str">
-        <v>7</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Digital Goods</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Sarang Dev</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>API Documentation</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Update the Swagger documentation for the latest API endpoints.</v>
-      </c>
-      <c r="C6" t="str">
-        <v>In Review</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E6" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="F6" t="str">
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="G6" t="str">
-        <v>Alex Smith</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Atul Bangre</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Security Patching</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Apply the latest security patches to the production servers.</v>
-      </c>
-      <c r="C7" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="D7" t="str">
-        <v>High</v>
-      </c>
-      <c r="E7" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="F7" t="str">
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="G7" t="str">
-        <v>Fakhri IT</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Sarang Dev</v>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+    <ignoredError sqref="A1:H1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>